--- a/data/atm_cost_effectiveness.xlsx
+++ b/data/atm_cost_effectiveness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23FC192-72D4-41C3-ACB8-03BF07CD58C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CCF35A-2CA9-43F9-828C-5FE4EB6E04F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="time_series" sheetId="2" r:id="rId1"/>
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -520,6 +520,48 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="C9" s="1">
+        <v>133</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="C10" s="1">
+        <v>142</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="C11" s="1">
+        <v>153</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -527,14 +569,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,27 +821,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1AB045E-407D-464E-B432-9331F7C58FF1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24F79C3-8935-4B5E-B87E-5CB91E86491B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -826,9 +859,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24F79C3-8935-4B5E-B87E-5CB91E86491B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1AB045E-407D-464E-B432-9331F7C58FF1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>